--- a/stories/arbres/TREE-FAM-021.xlsx
+++ b/stories/arbres/TREE-FAM-021.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élia est dans la cuisine. Un bocal est trop haut. C'est trop difficile. Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman. Maman écoute. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tabouret, l'évier, ou le placard.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près du tabouret, Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Près du tabouret, que fait Élia ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Élia a su aller vers eux. Elle a su dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Le bocal est haut. Élia va aller vers eux. Elle va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3414,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3581,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3748,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|La boîte. Élia va aller vers eux. Elle va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3939,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4106,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4273,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4440,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4607,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4774,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4941,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5108,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Le torchon. Élia va aller vers eux. Elle va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5299,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5466,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5633,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5800,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5967,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6134,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6301,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6468,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, Élia va aller vers eux. Elle va dire le besoin. Maman vient.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6649,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, que fait Élia ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6822,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Aller vers eux. Dire le besoin. Appeler maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7013,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7180,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, le bocal. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7371,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7538,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7705,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7872,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8039,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8206,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8373,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8540,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La boîte près de l'eau. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8731,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8898,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9065,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9232,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9399,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9566,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9733,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9900,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le torchon mouillé. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10091,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10258,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10425,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10592,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10759,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10926,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11093,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11260,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au placard, Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11441,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au placard, que fait Élia ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11614,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Élia a appelé. Elle a su dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11805,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11972,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au placard, le bocal. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12163,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12330,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12497,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12664,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12831,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +12998,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13165,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13332,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|La boîte du placard. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13523,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13690,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13857,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14024,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14191,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14358,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14525,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14692,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Le torchon du placard. Élia va aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14883,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15050,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15217,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15384,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15551,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15718,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15885,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15925,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-021.xlsx
+++ b/stories/arbres/TREE-FAM-021.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Élia est dans la cuisine. Un bocal est trop haut. C'est trop difficile. Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman. Maman écoute. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le tabouret, l'évier, ou le placard.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Près du tabouret, Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Près du tabouret, que fait Élia ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Élia a su aller vers eux. Elle a su dire le besoin.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Le bocal est haut. Élia va aller vers eux. Elle va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2751,6 +2764,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3100,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3419,6 +3436,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3586,6 +3604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3753,6 +3772,7 @@
           <t>narrateur|La boîte. Élia va aller vers eux. Elle va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3944,6 +3964,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4111,6 +4132,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4278,6 +4300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4445,6 +4468,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4612,6 +4636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4779,6 +4804,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4946,6 +4972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5113,6 +5140,7 @@
           <t>narrateur|Le torchon. Élia va aller vers eux. Elle va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5304,6 +5332,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5471,6 +5500,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5638,6 +5668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5805,6 +5836,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5972,6 +6004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6139,6 +6172,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à le tabouret. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6306,6 +6340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6473,6 +6508,7 @@
           <t>narrateur|À l'évier, Élia va aller vers eux. Elle va dire le besoin. Maman vient.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6656,6 +6692,7 @@
           <t>narrateur|À l'évier, que fait Élia ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6827,6 +6864,7 @@
           <t>narrateur|Oui. Aller vers eux. Dire le besoin. Appeler maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7018,6 +7056,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7185,6 +7224,7 @@
           <t>narrateur|À l'évier, le bocal. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7376,6 +7416,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7543,6 +7584,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7710,6 +7752,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7877,6 +7920,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8044,6 +8088,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8211,6 +8256,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8378,6 +8424,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8545,6 +8592,7 @@
           <t>narrateur|La boîte près de l'eau. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8736,6 +8784,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8903,6 +8952,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9070,6 +9120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9237,6 +9288,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9404,6 +9456,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9571,6 +9624,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9738,6 +9792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9905,6 +9960,7 @@
           <t>narrateur|Le torchon mouillé. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10096,6 +10152,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10263,6 +10320,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10430,6 +10488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10597,6 +10656,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10764,6 +10824,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10931,6 +10992,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à l'évier. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11098,6 +11160,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11265,6 +11328,7 @@
           <t>narrateur|Au placard, Élia va aller vers eux. Elle va dire le besoin. Elle appelle maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11448,6 +11512,7 @@
           <t>narrateur|Au placard, que fait Élia ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11619,6 +11684,7 @@
           <t>narrateur|Élia a appelé. Elle a su dire le besoin.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11810,6 +11876,7 @@
           <t>narrateur|On peut prendre le bocal, la boîte, ou le torchon.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11977,6 +12044,7 @@
           <t>narrateur|Au placard, le bocal. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12168,6 +12236,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12335,6 +12404,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12502,6 +12572,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12669,6 +12740,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12836,6 +12908,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13003,6 +13076,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le bocal, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13170,6 +13244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13337,6 +13412,7 @@
           <t>narrateur|La boîte du placard. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13528,6 +13604,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13695,6 +13772,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13862,6 +13940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14029,6 +14108,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14196,6 +14276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14363,6 +14444,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu la boîte, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14530,6 +14612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14697,6 +14780,7 @@
           <t>narrateur|Le torchon du placard. Élia va aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14888,6 +14972,7 @@
           <t>narrateur|On peut prendre un câlin, une aide, ou un mot.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15055,6 +15140,7 @@
           <t>narrateur|Élia rejoint un câlin. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15222,6 +15308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15389,6 +15476,7 @@
           <t>narrateur|Élia rejoint une aide. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,6 +15644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15723,6 +15812,7 @@
           <t>narrateur|Élia rejoint un mot. Elle a voulu le torchon, à le placard. Elle a su aller vers eux. Dire le besoin.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15890,6 +15980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15908,7 +15999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15932,6 +16023,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15946,7 +16051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16133,6 +16238,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
